--- a/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0001T0006Z000C1N8_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0001T0006Z000C1N8_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>37.39015309724126</v>
+        <v>6.075899878301705</v>
       </c>
       <c r="D2" t="n">
-        <v>24.74094373157906</v>
+        <v>4.020403356381597</v>
       </c>
       <c r="E2" t="n">
-        <v>11.38272929603242</v>
+        <v>1.849693510605269</v>
       </c>
       <c r="F2" t="n">
-        <v>11.22530316097874</v>
+        <v>1.824111763659046</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>17.54815612669068</v>
+        <v>2.851575370587235</v>
       </c>
       <c r="D3" t="n">
-        <v>17.76164632704169</v>
+        <v>2.886267528144274</v>
       </c>
       <c r="E3" t="n">
-        <v>11.38272929603242</v>
+        <v>1.849693510605269</v>
       </c>
       <c r="F3" t="n">
-        <v>11.22530316097874</v>
+        <v>1.824111763659046</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>24.7845634633166</v>
+        <v>4.027491562788947</v>
       </c>
       <c r="D4" t="n">
-        <v>25.00469128311871</v>
+        <v>4.063262333506791</v>
       </c>
       <c r="E4" t="n">
-        <v>11.38272929603242</v>
+        <v>1.849693510605269</v>
       </c>
       <c r="F4" t="n">
-        <v>11.22530316097874</v>
+        <v>1.824111763659046</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>14.70373041811554</v>
+        <v>2.389356192943775</v>
       </c>
       <c r="D5" t="n">
-        <v>14.87273688562853</v>
+        <v>2.416819743914637</v>
       </c>
       <c r="E5" t="n">
-        <v>11.38272929603242</v>
+        <v>1.849693510605269</v>
       </c>
       <c r="F5" t="n">
-        <v>11.22530316097874</v>
+        <v>1.824111763659046</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>48.57757178602817</v>
+        <v>7.893855415229578</v>
       </c>
       <c r="D6" t="n">
-        <v>48.45752848528737</v>
+        <v>7.874348378859198</v>
       </c>
       <c r="E6" t="n">
-        <v>11.38272929603242</v>
+        <v>1.849693510605269</v>
       </c>
       <c r="F6" t="n">
-        <v>11.22530316097874</v>
+        <v>1.824111763659046</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>40.05219789059416</v>
+        <v>6.508482157221551</v>
       </c>
       <c r="D7" t="n">
-        <v>39.92319285320832</v>
+        <v>6.487518838646352</v>
       </c>
       <c r="E7" t="n">
-        <v>11.38272929603242</v>
+        <v>1.849693510605269</v>
       </c>
       <c r="F7" t="n">
-        <v>11.22530316097874</v>
+        <v>1.824111763659046</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>19.99235965173807</v>
+        <v>3.248758443407437</v>
       </c>
       <c r="D8" t="n">
-        <v>35.00357124637428</v>
+        <v>5.68808032753582</v>
       </c>
       <c r="E8" t="n">
-        <v>11.38272929603242</v>
+        <v>1.849693510605269</v>
       </c>
       <c r="F8" t="n">
-        <v>11.22530316097874</v>
+        <v>1.824111763659046</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>34.80727669677163</v>
+        <v>5.65618246322539</v>
       </c>
       <c r="D9" t="n">
-        <v>34.88205013226046</v>
+        <v>5.668333146492325</v>
       </c>
       <c r="E9" t="n">
-        <v>11.38272929603242</v>
+        <v>1.849693510605269</v>
       </c>
       <c r="F9" t="n">
-        <v>11.22530316097874</v>
+        <v>1.824111763659046</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>16.29569173584679</v>
+        <v>2.648049907075104</v>
       </c>
       <c r="D10" t="n">
-        <v>16.42631991939632</v>
+        <v>2.669276986901902</v>
       </c>
       <c r="E10" t="n">
-        <v>11.38272929603242</v>
+        <v>1.849693510605269</v>
       </c>
       <c r="F10" t="n">
-        <v>11.22530316097874</v>
+        <v>1.824111763659046</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>33.54143374660329</v>
+        <v>5.450482983823035</v>
       </c>
       <c r="D11" t="n">
-        <v>46.07586399352613</v>
+        <v>7.487327898947996</v>
       </c>
       <c r="E11" t="n">
-        <v>11.38272929603242</v>
+        <v>1.849693510605269</v>
       </c>
       <c r="F11" t="n">
-        <v>11.22530316097874</v>
+        <v>1.824111763659046</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>34.23623349127458</v>
+        <v>5.56338794233212</v>
       </c>
       <c r="D12" t="n">
-        <v>16.32628095435469</v>
+        <v>2.653020655082637</v>
       </c>
       <c r="E12" t="n">
-        <v>11.38272929603242</v>
+        <v>1.849693510605269</v>
       </c>
       <c r="F12" t="n">
-        <v>11.22530316097874</v>
+        <v>1.824111763659046</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>49.42106332599483</v>
+        <v>8.030922790474159</v>
       </c>
       <c r="D13" t="n">
-        <v>28.71272695577946</v>
+        <v>4.665818130314162</v>
       </c>
       <c r="E13" t="n">
-        <v>11.38272929603242</v>
+        <v>1.849693510605269</v>
       </c>
       <c r="F13" t="n">
-        <v>11.22530316097874</v>
+        <v>1.824111763659046</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>22.92722389797274</v>
+        <v>3.72567388342057</v>
       </c>
       <c r="D14" t="n">
-        <v>18.65026278483841</v>
+        <v>3.030667702536241</v>
       </c>
       <c r="E14" t="n">
-        <v>11.38272929603242</v>
+        <v>1.849693510605269</v>
       </c>
       <c r="F14" t="n">
-        <v>11.22530316097874</v>
+        <v>1.824111763659046</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
